--- a/stories/arbres/ATOM-SOC.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes. Papa dit : c'est un métier. Zélie dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur. Papa dit : c'est un métier. Zélie dit : médecin. Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire. Papa dit : c'est un métier. Zélie dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus. Zélie dit : chauffeur. C'est un métier. Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
+          <t>Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus. Chauffeur. C'est un métier. Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes.
+papa|C'est un métier.
+enfant-f|Boulanger.
+narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur.
+papa|C'est un métier.
+enfant-f|Médecin.
+narrateur|Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire.
+papa|C'est un métier.
+enfant-f|Maîtresse.
+narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus.
+enfant-f|Chauffeur. C'est un métier.
+narrateur|Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le boulanger fait du pain. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Zélie a nommé les métiers. Boulanger. Médecin. Maîtresse. Chauffeur. Chaque geste est utile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1837,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Zélie serre la main de papa. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2004,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2044,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Le boulanger fait du pain. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Zélie a nommé les métiers. Boulanger. Médecin. Maîtresse. Chauffeur. Chaque geste est utile.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1842,6 +1850,7 @@
           <t>narrateur|Zélie serre la main de papa. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2009,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2051,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2252,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zélie nomme les métiers</t>
+          <t>L'arrosoir du square</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut une petite plante pour la fenêtre. L'arrosoir penche. L'horticultrice du square tend un pot. Puis le boulanger glisse un pain rond dans le sac.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus. Chauffeur. C'est un métier. Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
+          <t>Un arrosoir laisse une goutte sur la pierre. La goutte brille, puis elle file dans une fissure. Le square sent la terre mouillée et la menthe. Mila vit ici, tout près, avec papa. Un banc de bois encore froid attend sous le tilleul. Je veux une petite plante, papa. Pour la fenêtre. On demande à l'horticultrice ? Celle du square. Oui. En ce moment, Mila suit la trace d'eau sur les dalles. Les dalles sont rudes, un peu vertes. L'horticultrice est accroupie près des géraniums. Ses gants sont bruns, collés de terre. Elle arrose. C'est l'horticultrice. C'est son métier. Elle soigne les plantes. Oui. Mila s'arrête trop près de l'arrosoir. L'arrosoir penche. Un filet d'eau part vers la chaussure de papa. Oh. On recule un peu. Pardon. On reste sur la dalle sèche ? Oui. L'horticultrice redresse l'arrosoir. Elle tend un petit pot, terre encore sombre. Une feuille ronde, toute neuve, au milieu. Pour la fenêtre ? Si tu la portes sans la serrer. Mila prend le pot à deux mains. La terre sent le jardin, tout fort. Merci. Merci. Bravo, Mila. Tu as trouvé l'horticultrice. J'ai faim, maintenant. Le boulanger est juste après le square.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes. Papa dit : c'est un &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;. Zélie dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur. Papa dit : c'est un métier. Zélie dit : médecin. Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire. Papa dit : c'est un métier. Zélie dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus. Zélie dit : chauffeur. C'est un métier. Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un arrosoir laisse une goutte sur la pierre. La goutte brille, puis elle file dans une fissure. Le square sent la terre mouillée et la menthe. Mila vit ici, tout près, avec papa. Un banc de bois encore froid attend sous le tilleul. Je veux une petite plante, papa. Pour la fenêtre. On demande à l'horticultrice ? Celle du square. Oui. En ce moment, Mila suit la trace d'eau sur les dalles. Les dalles sont rudes, un peu vertes. L'horticultrice est accroupie près des géraniums. Ses gants sont bruns, collés de terre. Elle arrose. C'est l'horticultrice. C'est son métier. Elle soigne les plantes. Oui. Mila s'arrête trop près de l'arrosoir. L'arrosoir penche. Un filet d'eau part vers la chaussure de papa. Oh. On recule un peu. Pardon. On reste sur la dalle sèche ? Oui. L'horticultrice redresse l'arrosoir. Elle tend un petit pot, terre encore sombre. Une feuille ronde, toute neuve, au milieu. Pour la fenêtre ? Si tu la portes sans la serrer. Mila prend le pot à deux mains. La terre sent le jardin, tout fort. Merci. Merci. Bravo, Mila. Tu as trouvé l'horticultrice. J'ai faim, maintenant. Le boulanger est juste après le square.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,21 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Zélie marche avec papa. Ils sentent le pain chaud. Le boulanger pose les baguettes.
-papa|C'est un métier.
-enfant-f|Boulanger.
-narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ensuite, ils passent chez le médecin. Le médecin écoute le cœur.
-papa|C'est un métier.
-enfant-f|Médecin.
-narrateur|Le médecin fait un geste utile. Il soigne. Après, la maîtresse lit une histoire.
-papa|C'est un métier.
-enfant-f|Maîtresse.
-narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Plus tard, un chauffeur arrête le bus.
-enfant-f|Chauffeur. C'est un métier.
-narrateur|Le chauffeur fait un geste utile. Il emmène les gens. Chaque métier a un geste utile.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un arrosoir laisse une goutte sur la pierre.
+narrateur|La goutte brille, puis elle file dans une fissure.
+narrateur|Le square sent la terre mouillée et la menthe.
+narrateur|Mila vit ici, tout près, avec papa.
+narrateur|Un banc de bois encore froid attend sous le tilleul.
+enfant-f|Je veux une petite plante, papa.
+enfant-f|Pour la fenêtre.
+papa|On demande à l'horticultrice ?
+enfant-f|Celle du square.
+papa|Oui.
+narrateur|En ce moment, Mila suit la trace d'eau sur les dalles.
+narrateur|Les dalles sont rudes, un peu vertes.
+narrateur|L'horticultrice est accroupie près des géraniums.
+narrateur|Ses gants sont bruns, collés de terre.
+enfant-f|Elle arrose.
+papa|C'est l'horticultrice.
+papa|C'est son métier.
+enfant-f|Elle soigne les plantes.
+papa|Oui.
+narrateur|Mila s'arrête trop près de l'arrosoir.
+narrateur|L'arrosoir penche.
+narrateur|Un filet d'eau part vers la chaussure de papa.
+papa|Oh.
+papa|On recule un peu.
+enfant-f|Pardon.
+papa|On reste sur la dalle sèche ?
+enfant-f|Oui.
+narrateur|L'horticultrice redresse l'arrosoir.
+narrateur|Elle tend un petit pot, terre encore sombre.
+narrateur|Une feuille ronde, toute neuve, au milieu.
+enfant-f|Pour la fenêtre ?
+papa|Si tu la portes sans la serrer.
+narrateur|Mila prend le pot à deux mains.
+narrateur|La terre sent le jardin, tout fort.
+papa|Merci.
+enfant-f|Merci.
+papa|Bravo, Mila.
+papa|Tu as trouvé l'horticultrice.
+enfant-f|J'ai faim, maintenant.
+papa|Le boulanger est juste après le square.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1351,27 +1390,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>L'horticultrice arrose les plantes. C'est quoi ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L'horticultrice arrose les plantes. C'est quoi ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Le boulanger fait du pain. C'est quoi ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le boulanger fait du pain. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Le boulanger fait du pain. C'est quoi ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>un métier</t>
+          <t>métier</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>un métier | métier | boulanger | le boulanger</t>
+          <t>métier | un métier | son métier | le métier | c'est un métier</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1386,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il fait un geste utile. C'est quoi ?</t>
+          <t>Elle soigne les plantes. C'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,14 +1467,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le boulanger fait du pain. C'est quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|L'horticultrice arrose les plantes.
+narrateur|C'est quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Zélie a nommé les métiers. Boulanger. Médecin. Maîtresse. Chauffeur. Chaque geste est utile.</t>
+          <t>Ils longent la grille, le pot bien droit. Une feuille tape le menton de Mila. La boutique du pain ouvre ses deux battants. Ça sent le sésame et la croûte. Le boulanger ! Oui. Lui aussi a un métier. Le pain. Il prépare le pain. Mila pose le pot sur le bord du comptoir. Le boulanger farine ses mains, encore. Un pain rond, un peu doré, part dans le sac. Merci. Le pot, je le reprends. Les deux, plante et pain. Le sac tape la hanche, tout léger. La feuille ronde tremble à chaque pas. Tu tiens bien ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zélie a nommé les &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;s. Boulanger. Médecin. Maîtresse. Chauffeur. Chaque geste est utile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils longent la grille, le pot bien droit. Une feuille tape le menton de Mila. La boutique du pain ouvre ses deux battants. Ça sent le sésame et la croûte. Le boulanger ! Oui. Lui aussi a un métier. Le pain. Il prépare le pain. Mila pose le pot sur le bord du comptoir. Le boulanger farine ses mains, encore. Un pain rond, un peu doré, part dans le sac. Merci. Le pot, je le reprends. Les deux, plante et pain. Le sac tape la hanche, tout léger. La feuille ronde tremble à chaque pas. Tu tiens bien ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1642,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1718,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Zélie a nommé les métiers. Boulanger. Médecin. Maîtresse. Chauffeur. Chaque geste est utile.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Ils longent la grille, le pot bien droit.
+narrateur|Une feuille tape le menton de Mila.
+narrateur|La boutique du pain ouvre ses deux battants.
+narrateur|Ça sent le sésame et la croûte.
+enfant-f|Le boulanger !
+papa|Oui.
+papa|Lui aussi a un métier.
+enfant-f|Le pain.
+papa|Il prépare le pain.
+narrateur|Mila pose le pot sur le bord du comptoir.
+narrateur|Le boulanger farine ses mains, encore.
+narrateur|Un pain rond, un peu doré, part dans le sac.
+papa|Merci.
+enfant-f|Le pot, je le reprends.
+papa|Les deux, plante et pain.
+narrateur|Le sac tape la hanche, tout léger.
+narrateur|La feuille ronde tremble à chaque pas.
+papa|Tu tiens bien ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Zélie serre la main de papa. Ils rentrent à la maison.</t>
+          <t>La fenêtre de la cuisine est déjà ouverte. Un peu de vent entre, avec la menthe du square. Mila pose le pot sur le rebord. La terre reste sombre, bien tenue. Elle voit le square, d'ici. Oui. L'horticultrice l'a choisie pour toi. Papa coupe le pain rond. La mie est blanche, encore tiède. Un morceau près du pot ? Pour moi. Pour toi. La plante boit l'eau, pas le pain. Je le savais. Merci d'avoir porté le pot sans le serrer.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Zélie serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fenêtre de la cuisine est déjà ouverte. Un peu de vent entre, avec la menthe du square. Mila pose le pot sur le rebord. La terre reste sombre, bien tenue. Elle voit le square, d'ici. Oui. L'horticultrice l'a choisie pour toi. Papa coupe le pain rond. La mie est blanche, encore tiède. Un morceau près du pot ? Pour moi. Pour toi. La plante boit l'eau, pas le pain. Je le savais. Merci d'avoir porté le pot sans le serrer.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1831,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1847,10 +1903,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Zélie serre la main de papa. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La fenêtre de la cuisine est déjà ouverte.
+narrateur|Un peu de vent entre, avec la menthe du square.
+narrateur|Mila pose le pot sur le rebord.
+narrateur|La terre reste sombre, bien tenue.
+enfant-f|Elle voit le square, d'ici.
+papa|Oui.
+papa|L'horticultrice l'a choisie pour toi.
+narrateur|Papa coupe le pain rond.
+narrateur|La mie est blanche, encore tiède.
+papa|Un morceau près du pot ?
+enfant-f|Pour moi.
+papa|Pour toi.
+papa|La plante boit l'eau, pas le pain.
+enfant-f|Je le savais.
+papa|Merci d'avoir porté le pot sans le serrer.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1875,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La feuille ronde tourne vers le jour. Une goutte reste encore sur la terre. Elle est bien, là. Oui. Le square continue, tout près, avec son arrosoir. Le pain tiède sent le sésame, sur la table. La fenêtre garde la petite plante, et le vent.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La feuille ronde tourne vers le jour. Une goutte reste encore sur la terre. Elle est bien, là. Oui. Le square continue, tout près, avec son arrosoir. Le pain tiède sent le sésame, sur la table. La fenêtre garde la petite plante, et le vent.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1943,7 +2012,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2015,10 +2084,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La feuille ronde tourne vers le jour.
+narrateur|Une goutte reste encore sur la terre.
+enfant-f|Elle est bien, là.
+papa|Oui.
+narrateur|Le square continue, tout près, avec son arrosoir.
+narrateur|Le pain tiède sent le sésame, sur la table.
+narrateur|La fenêtre garde la petite plante, et le vent.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2037,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quartier</t>
+          <t>square du village, terre mouillée, puis boutique du pain, fenêtre de la cuisine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zélie, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
